--- a/FLORES DE ESTRADA/Mayo/EDESUR MAYO.xlsx
+++ b/FLORES DE ESTRADA/Mayo/EDESUR MAYO.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OneDrive\Desktop\RC CONSORCIO 2025\FLORES DE ESTRADA\Mayo\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2363AD6B-02EC-4E41-87F6-C3532154565F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{86A27130-77C1-4323-87DA-2113D9E96FB0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -334,7 +334,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="9">
+  <fills count="10">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -379,7 +379,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
+        <fgColor rgb="FFFF0000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF0000"/>
         <bgColor theme="0"/>
       </patternFill>
     </fill>
@@ -542,7 +548,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="64">
+  <cellXfs count="69">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -616,8 +622,9 @@
     <xf numFmtId="2" fontId="4" fillId="7" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="4" fillId="7" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="7" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="4" fillId="8" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="8" fillId="5" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="12" fillId="5" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -633,8 +640,12 @@
     <xf numFmtId="0" fontId="11" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="12" fillId="5" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="4" fillId="8" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="4" fillId="8" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="4" fillId="8" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="4" fillId="9" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -939,7 +950,7 @@
     <col min="2" max="2" width="10" customWidth="1"/>
     <col min="3" max="3" width="14.85546875" customWidth="1"/>
     <col min="4" max="4" width="27" customWidth="1"/>
-    <col min="5" max="5" width="0.140625" customWidth="1"/>
+    <col min="5" max="5" width="6.42578125" customWidth="1"/>
     <col min="6" max="6" width="10.42578125" hidden="1" customWidth="1"/>
     <col min="7" max="7" width="10" hidden="1" customWidth="1"/>
     <col min="8" max="8" width="7.7109375" hidden="1" customWidth="1"/>
@@ -959,21 +970,21 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:25" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="55" t="s">
+      <c r="A1" s="56" t="s">
         <v>65</v>
       </c>
-      <c r="B1" s="56"/>
-      <c r="C1" s="56"/>
-      <c r="D1" s="56"/>
-      <c r="E1" s="56"/>
-      <c r="F1" s="56"/>
-      <c r="G1" s="56"/>
-      <c r="H1" s="56"/>
-      <c r="I1" s="56"/>
-      <c r="J1" s="56"/>
-      <c r="K1" s="56"/>
-      <c r="L1" s="56"/>
-      <c r="M1" s="57"/>
+      <c r="B1" s="57"/>
+      <c r="C1" s="57"/>
+      <c r="D1" s="57"/>
+      <c r="E1" s="57"/>
+      <c r="F1" s="57"/>
+      <c r="G1" s="57"/>
+      <c r="H1" s="57"/>
+      <c r="I1" s="57"/>
+      <c r="J1" s="57"/>
+      <c r="K1" s="57"/>
+      <c r="L1" s="57"/>
+      <c r="M1" s="58"/>
       <c r="N1" s="1"/>
       <c r="O1" s="2"/>
       <c r="P1" s="3"/>
@@ -1115,7 +1126,7 @@
       <c r="B8" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="C8" s="62">
+      <c r="C8" s="54">
         <f>23662 +1419829.7</f>
         <v>1443491.7</v>
       </c>
@@ -1250,45 +1261,45 @@
       <c r="A11" s="18">
         <v>2</v>
       </c>
-      <c r="B11" s="37">
+      <c r="B11" s="63">
         <v>2</v>
       </c>
-      <c r="C11" s="37" t="s">
+      <c r="C11" s="63" t="s">
         <v>24</v>
       </c>
-      <c r="D11" s="37" t="s">
+      <c r="D11" s="63" t="s">
         <v>25</v>
       </c>
-      <c r="E11" s="37">
+      <c r="E11" s="63">
         <v>3.89</v>
       </c>
-      <c r="F11" s="37">
+      <c r="F11" s="63">
         <v>16863.900000000001</v>
       </c>
-      <c r="G11" s="42">
+      <c r="G11" s="64">
         <f>F11+70</f>
         <v>16933.900000000001</v>
       </c>
-      <c r="H11" s="38">
-        <v>0</v>
-      </c>
-      <c r="I11" s="39">
+      <c r="H11" s="65">
+        <v>0</v>
+      </c>
+      <c r="I11" s="66">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J11" s="39">
+      <c r="J11" s="66">
         <f>(G11-F11)*93.78</f>
         <v>6564.6</v>
       </c>
-      <c r="K11" s="40">
+      <c r="K11" s="67">
         <f t="shared" ref="K11:K25" si="2">G11-F11</f>
         <v>70</v>
       </c>
-      <c r="L11" s="38">
+      <c r="L11" s="65">
         <f>L9*E11/100</f>
         <v>44575.823775180019</v>
       </c>
-      <c r="M11" s="38">
+      <c r="M11" s="65">
         <f t="shared" ref="M11:M24" si="3">J11+L11+1</f>
         <v>51141.423775180017</v>
       </c>
@@ -1689,7 +1700,7 @@
       <c r="G18" s="41">
         <v>19975.5</v>
       </c>
-      <c r="H18" s="54">
+      <c r="H18" s="53">
         <v>0</v>
       </c>
       <c r="I18" s="45">
@@ -1852,7 +1863,7 @@
       <c r="C21" s="43" t="s">
         <v>43</v>
       </c>
-      <c r="D21" s="63" t="s">
+      <c r="D21" s="55" t="s">
         <v>64</v>
       </c>
       <c r="E21" s="43">
@@ -1908,45 +1919,45 @@
       <c r="A22" s="43">
         <v>13</v>
       </c>
-      <c r="B22" s="37">
+      <c r="B22" s="63">
         <v>13</v>
       </c>
-      <c r="C22" s="37" t="s">
+      <c r="C22" s="63" t="s">
         <v>45</v>
       </c>
-      <c r="D22" s="37" t="s">
+      <c r="D22" s="63" t="s">
         <v>46</v>
       </c>
-      <c r="E22" s="37">
+      <c r="E22" s="63">
         <v>4.45</v>
       </c>
-      <c r="F22" s="37">
+      <c r="F22" s="63">
         <v>10672.2</v>
       </c>
-      <c r="G22" s="42">
+      <c r="G22" s="64">
         <f>F22+193-30</f>
         <v>10835.2</v>
       </c>
-      <c r="H22" s="53">
-        <v>0</v>
-      </c>
-      <c r="I22" s="39">
+      <c r="H22" s="68">
+        <v>0</v>
+      </c>
+      <c r="I22" s="66">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J22" s="39">
+      <c r="J22" s="66">
         <f t="shared" si="5"/>
         <v>15286.14</v>
       </c>
-      <c r="K22" s="40">
+      <c r="K22" s="67">
         <f t="shared" si="2"/>
         <v>163</v>
       </c>
-      <c r="L22" s="38">
+      <c r="L22" s="65">
         <f>L9*E22/100</f>
         <v>50992.908945900024</v>
       </c>
-      <c r="M22" s="38">
+      <c r="M22" s="65">
         <f t="shared" si="3"/>
         <v>66280.048945900024</v>
       </c>
@@ -2536,7 +2547,7 @@
       <c r="C33" s="43" t="s">
         <v>60</v>
       </c>
-      <c r="D33" s="63" t="s">
+      <c r="D33" s="55" t="s">
         <v>64</v>
       </c>
       <c r="E33" s="43">
@@ -2622,19 +2633,19 @@
       <c r="A35" s="31" t="s">
         <v>61</v>
       </c>
-      <c r="C35" s="58" t="s">
+      <c r="C35" s="59" t="s">
         <v>62</v>
       </c>
-      <c r="D35" s="56"/>
-      <c r="E35" s="56"/>
-      <c r="F35" s="56"/>
-      <c r="G35" s="56"/>
-      <c r="H35" s="56"/>
-      <c r="I35" s="56"/>
-      <c r="J35" s="56"/>
-      <c r="K35" s="56"/>
-      <c r="L35" s="56"/>
-      <c r="M35" s="59"/>
+      <c r="D35" s="57"/>
+      <c r="E35" s="57"/>
+      <c r="F35" s="57"/>
+      <c r="G35" s="57"/>
+      <c r="H35" s="57"/>
+      <c r="I35" s="57"/>
+      <c r="J35" s="57"/>
+      <c r="K35" s="57"/>
+      <c r="L35" s="57"/>
+      <c r="M35" s="60"/>
       <c r="N35" s="31"/>
       <c r="O35" s="2" t="e">
         <f t="shared" si="9"/>
@@ -2658,80 +2669,80 @@
       <c r="O37" s="2"/>
     </row>
     <row r="38" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B38" s="60" t="s">
+      <c r="B38" s="61" t="s">
         <v>66</v>
       </c>
-      <c r="C38" s="61"/>
-      <c r="D38" s="61"/>
-      <c r="E38" s="61"/>
-      <c r="F38" s="61"/>
-      <c r="G38" s="61"/>
-      <c r="H38" s="61"/>
-      <c r="I38" s="61"/>
-      <c r="J38" s="61"/>
-      <c r="K38" s="61"/>
-      <c r="L38" s="61"/>
-      <c r="M38" s="61"/>
+      <c r="C38" s="62"/>
+      <c r="D38" s="62"/>
+      <c r="E38" s="62"/>
+      <c r="F38" s="62"/>
+      <c r="G38" s="62"/>
+      <c r="H38" s="62"/>
+      <c r="I38" s="62"/>
+      <c r="J38" s="62"/>
+      <c r="K38" s="62"/>
+      <c r="L38" s="62"/>
+      <c r="M38" s="62"/>
       <c r="O38" s="2"/>
     </row>
     <row r="39" spans="1:16" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B39" s="61"/>
-      <c r="C39" s="61"/>
-      <c r="D39" s="61"/>
-      <c r="E39" s="61"/>
-      <c r="F39" s="61"/>
-      <c r="G39" s="61"/>
-      <c r="H39" s="61"/>
-      <c r="I39" s="61"/>
-      <c r="J39" s="61"/>
-      <c r="K39" s="61"/>
-      <c r="L39" s="61"/>
-      <c r="M39" s="61"/>
+      <c r="B39" s="62"/>
+      <c r="C39" s="62"/>
+      <c r="D39" s="62"/>
+      <c r="E39" s="62"/>
+      <c r="F39" s="62"/>
+      <c r="G39" s="62"/>
+      <c r="H39" s="62"/>
+      <c r="I39" s="62"/>
+      <c r="J39" s="62"/>
+      <c r="K39" s="62"/>
+      <c r="L39" s="62"/>
+      <c r="M39" s="62"/>
       <c r="O39" s="2"/>
     </row>
     <row r="40" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B40" s="61"/>
-      <c r="C40" s="61"/>
-      <c r="D40" s="61"/>
-      <c r="E40" s="61"/>
-      <c r="F40" s="61"/>
-      <c r="G40" s="61"/>
-      <c r="H40" s="61"/>
-      <c r="I40" s="61"/>
-      <c r="J40" s="61"/>
-      <c r="K40" s="61"/>
-      <c r="L40" s="61"/>
-      <c r="M40" s="61"/>
+      <c r="B40" s="62"/>
+      <c r="C40" s="62"/>
+      <c r="D40" s="62"/>
+      <c r="E40" s="62"/>
+      <c r="F40" s="62"/>
+      <c r="G40" s="62"/>
+      <c r="H40" s="62"/>
+      <c r="I40" s="62"/>
+      <c r="J40" s="62"/>
+      <c r="K40" s="62"/>
+      <c r="L40" s="62"/>
+      <c r="M40" s="62"/>
       <c r="O40" s="2"/>
     </row>
     <row r="41" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B41" s="61"/>
-      <c r="C41" s="61"/>
-      <c r="D41" s="61"/>
-      <c r="E41" s="61"/>
-      <c r="F41" s="61"/>
-      <c r="G41" s="61"/>
-      <c r="H41" s="61"/>
-      <c r="I41" s="61"/>
-      <c r="J41" s="61"/>
-      <c r="K41" s="61"/>
-      <c r="L41" s="61"/>
-      <c r="M41" s="61"/>
+      <c r="B41" s="62"/>
+      <c r="C41" s="62"/>
+      <c r="D41" s="62"/>
+      <c r="E41" s="62"/>
+      <c r="F41" s="62"/>
+      <c r="G41" s="62"/>
+      <c r="H41" s="62"/>
+      <c r="I41" s="62"/>
+      <c r="J41" s="62"/>
+      <c r="K41" s="62"/>
+      <c r="L41" s="62"/>
+      <c r="M41" s="62"/>
       <c r="O41" s="2"/>
     </row>
     <row r="42" spans="1:16" ht="64.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B42" s="61"/>
-      <c r="C42" s="61"/>
-      <c r="D42" s="61"/>
-      <c r="E42" s="61"/>
-      <c r="F42" s="61"/>
-      <c r="G42" s="61"/>
-      <c r="H42" s="61"/>
-      <c r="I42" s="61"/>
-      <c r="J42" s="61"/>
-      <c r="K42" s="61"/>
-      <c r="L42" s="61"/>
-      <c r="M42" s="61"/>
+      <c r="B42" s="62"/>
+      <c r="C42" s="62"/>
+      <c r="D42" s="62"/>
+      <c r="E42" s="62"/>
+      <c r="F42" s="62"/>
+      <c r="G42" s="62"/>
+      <c r="H42" s="62"/>
+      <c r="I42" s="62"/>
+      <c r="J42" s="62"/>
+      <c r="K42" s="62"/>
+      <c r="L42" s="62"/>
+      <c r="M42" s="62"/>
       <c r="O42" s="2"/>
     </row>
     <row r="43" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -6603,21 +6614,21 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:18" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="55" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="56"/>
-      <c r="C1" s="56"/>
-      <c r="D1" s="56"/>
-      <c r="E1" s="56"/>
-      <c r="F1" s="56"/>
-      <c r="G1" s="56"/>
-      <c r="H1" s="56"/>
-      <c r="I1" s="56"/>
-      <c r="J1" s="56"/>
-      <c r="K1" s="56"/>
-      <c r="L1" s="56"/>
-      <c r="M1" s="57"/>
+      <c r="A1" s="56" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="57"/>
+      <c r="C1" s="57"/>
+      <c r="D1" s="57"/>
+      <c r="E1" s="57"/>
+      <c r="F1" s="57"/>
+      <c r="G1" s="57"/>
+      <c r="H1" s="57"/>
+      <c r="I1" s="57"/>
+      <c r="J1" s="57"/>
+      <c r="K1" s="57"/>
+      <c r="L1" s="57"/>
+      <c r="M1" s="58"/>
       <c r="N1" s="1"/>
       <c r="O1" s="2"/>
       <c r="P1" s="3"/>
@@ -8209,19 +8220,19 @@
       <c r="A35" s="31" t="s">
         <v>61</v>
       </c>
-      <c r="C35" s="58" t="s">
+      <c r="C35" s="59" t="s">
         <v>62</v>
       </c>
-      <c r="D35" s="56"/>
-      <c r="E35" s="56"/>
-      <c r="F35" s="56"/>
-      <c r="G35" s="56"/>
-      <c r="H35" s="56"/>
-      <c r="I35" s="56"/>
-      <c r="J35" s="56"/>
-      <c r="K35" s="56"/>
-      <c r="L35" s="56"/>
-      <c r="M35" s="59"/>
+      <c r="D35" s="57"/>
+      <c r="E35" s="57"/>
+      <c r="F35" s="57"/>
+      <c r="G35" s="57"/>
+      <c r="H35" s="57"/>
+      <c r="I35" s="57"/>
+      <c r="J35" s="57"/>
+      <c r="K35" s="57"/>
+      <c r="L35" s="57"/>
+      <c r="M35" s="60"/>
       <c r="N35" s="31"/>
       <c r="O35" s="2" t="e">
         <f t="shared" si="8"/>
